--- a/data/trans_dic/P42C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P42C_R-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -516,39 +516,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya última consulta ginecológica fue en un centro privado</t>
+          <t>Población cuya última consulta ginecológica fue en un centro privado (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -579,21 +569,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -608,9 +583,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -625,17 +597,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,21 +621,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33,64%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>45,72%</t>
         </is>
@@ -678,47 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,17; 49,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,7; 39,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,84; 51,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,11; 49,61</t>
+          <t>37,17; 49,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,82; 39,87</t>
+          <t>28,7; 39,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,82; 50,99</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,11; 49,61</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28,82; 39,87</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>40,82; 50,99</t>
+          <t>40,84; 51,37</t>
         </is>
       </c>
     </row>
@@ -735,17 +677,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,21 +701,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>43,18%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>41,29%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>43,18%</t>
         </is>
@@ -788,47 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,6; 47,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,91; 33,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,67; 48,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,28; 48,1</t>
+          <t>34,6; 47,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,27; 33,49</t>
+          <t>22,91; 33,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,81; 48,95</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,28; 48,1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>23,27; 33,49</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>37,81; 48,95</t>
+          <t>37,67; 48,48</t>
         </is>
       </c>
     </row>
@@ -845,17 +757,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,21 +781,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>22,62%</t>
         </is>
@@ -898,47 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,43; 33,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,72; 17,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,92; 30,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,56; 32,83</t>
+          <t>20,43; 33,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 17,41</t>
+          <t>6,72; 17,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,15; 29,82</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>20,56; 32,83</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6,89; 17,41</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>16,15; 29,82</t>
+          <t>15,92; 30,47</t>
         </is>
       </c>
     </row>
@@ -955,17 +837,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,21 +861,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>21,03%</t>
         </is>
@@ -1008,47 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,55; 25,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,67; 17,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,71; 25,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,67; 25,7</t>
+          <t>18,55; 25,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,51; 17,11</t>
+          <t>11,67; 17,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,7; 24,46</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18,67; 25,7</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11,51; 17,11</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>17,7; 24,46</t>
+          <t>17,71; 25,08</t>
         </is>
       </c>
     </row>
@@ -1065,17 +917,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1089,21 +941,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>9,56%</t>
         </is>
@@ -1118,47 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,53; 18,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,56; 9,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,29; 12,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,74; 19,11</t>
+          <t>12,53; 18,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,13</t>
+          <t>4,56; 9,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 12,46</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,74; 19,11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4,64; 9,13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5,94; 12,46</t>
+          <t>6,29; 12,73</t>
         </is>
       </c>
     </row>
@@ -1175,17 +997,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1199,21 +1021,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>14,08%</t>
         </is>
@@ -1228,47 +1035,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,94; 20,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,92; 13,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,05; 18,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,95; 20,68</t>
+          <t>14,94; 20,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,88; 13,69</t>
+          <t>8,92; 13,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,06; 17,49</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>14,95; 20,68</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>8,88; 13,69</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>11,06; 17,49</t>
+          <t>11,05; 18,29</t>
         </is>
       </c>
     </row>
@@ -1285,17 +1077,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1309,21 +1101,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15,45%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>22,72%</t>
         </is>
@@ -1338,47 +1115,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,19; 25,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,03; 16,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,06; 24,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,2; 25,57</t>
+          <t>22,19; 25,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,08; 16,95</t>
+          <t>14,03; 16,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,61; 24,66</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>22,2; 25,57</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>14,08; 16,95</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>19,61; 24,66</t>
+          <t>20,06; 24,85</t>
         </is>
       </c>
     </row>
@@ -1390,13 +1152,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
@@ -1413,7 +1174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1424,39 +1185,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya última consulta ginecológica fue en un centro privado</t>
+          <t>Población cuya última consulta ginecológica fue en un centro privado (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1487,21 +1238,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1516,9 +1252,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1533,17 +1266,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>107</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1557,21 +1290,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>201</t>
         </is>
@@ -1586,17 +1304,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121809</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>103761</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1610,21 +1328,6 @@
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>124871</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>121809</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>103761</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>124871</t>
         </is>
@@ -1639,47 +1342,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>105390; 140233</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88529; 122197</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>111561; 140322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105195; 140632</t>
+          <t>105390; 140233</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>88909; 122970</t>
+          <t>88529; 122197</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>111512; 139291</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>105195; 140632</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>88909; 122970</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>111512; 139291</t>
+          <t>111561; 140322</t>
         </is>
       </c>
     </row>
@@ -1696,17 +1384,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1720,21 +1408,6 @@
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
@@ -1749,17 +1422,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116567</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92676</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102447</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1773,21 +1446,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>102447</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>116567</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>92676</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>102447</t>
         </is>
@@ -1802,47 +1460,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>97679; 134602</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>76550; 111193</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89357; 115003</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99621; 135820</t>
+          <t>97679; 134602</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77755; 111915</t>
+          <t>76550; 111193</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89703; 116126</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>99621; 135820</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>77755; 111915</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>89703; 116126</t>
+          <t>89357; 115003</t>
         </is>
       </c>
     </row>
@@ -1859,17 +1502,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1883,21 +1526,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -1912,17 +1540,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56867</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1936,21 +1564,6 @@
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21561</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>56867</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>15864</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>21561</t>
         </is>
@@ -1965,47 +1578,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43975; 71308</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9528; 25031</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15175; 29037</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44252; 70680</t>
+          <t>43975; 71308</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9771; 24690</t>
+          <t>9528; 25031</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15388; 28419</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>44252; 70680</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9771; 24690</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15388; 28419</t>
+          <t>15175; 29037</t>
         </is>
       </c>
     </row>
@@ -2022,17 +1620,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2046,21 +1644,6 @@
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>134</t>
         </is>
@@ -2075,17 +1658,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135138</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98542</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94031</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2099,21 +1682,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94031</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>135138</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>98542</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>94031</t>
         </is>
@@ -2128,47 +1696,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>114414; 158983</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80406; 118904</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>79189; 112135</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>115153; 158500</t>
+          <t>114414; 158983</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>79334; 117911</t>
+          <t>80406; 118904</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79153; 109344</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>115153; 158500</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>79334; 117911</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79153; 109344</t>
+          <t>79189; 112135</t>
         </is>
       </c>
     </row>
@@ -2185,17 +1738,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2209,21 +1762,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
@@ -2238,17 +1776,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93327</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36950</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2262,21 +1800,6 @@
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93327</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>36950</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>51237</t>
         </is>
@@ -2291,47 +1814,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74912; 112071</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25911; 51429</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33710; 68247</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76206; 114251</t>
+          <t>74912; 112071</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26348; 51857</t>
+          <t>25911; 51429</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31866; 66779</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>76206; 114251</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>26348; 51857</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>31866; 66779</t>
+          <t>33710; 68247</t>
         </is>
       </c>
     </row>
@@ -2348,17 +1856,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2372,21 +1880,6 @@
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
@@ -2401,17 +1894,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>130975</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79415</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53966</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2425,21 +1918,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>53966</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>130975</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>79415</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53966</t>
         </is>
@@ -2454,47 +1932,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>110579; 152074</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64656; 98221</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42349; 70111</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>110618; 153090</t>
+          <t>110579; 152074</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>64331; 99216</t>
+          <t>64656; 98221</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42412; 67048</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>110618; 153090</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>64331; 99216</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>42412; 67048</t>
+          <t>42349; 70111</t>
         </is>
       </c>
     </row>
@@ -2511,17 +1974,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>402</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2535,21 +1998,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>684</t>
         </is>
@@ -2564,17 +2012,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>654683</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>427208</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>448113</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2588,21 +2036,6 @@
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>448113</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>654683</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>427208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>448113</t>
         </is>
@@ -2617,47 +2050,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>607037; 703914</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>388046; 464711</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>395698; 490137</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>607333; 699439</t>
+          <t>607037; 703914</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>389544; 468838</t>
+          <t>388046; 464711</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>386847; 486282</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>607333; 699439</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>389544; 468838</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>386847; 486282</t>
+          <t>395698; 490137</t>
         </is>
       </c>
     </row>
@@ -2669,14 +2087,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>

--- a/data/trans_dic/P42C_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P42C_R-Clase-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,89%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,17; 49,47</t>
+          <t>36,78; 49,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,7; 39,62</t>
+          <t>28,33; 39,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,84; 51,37</t>
+          <t>40,85; 50,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,17; 49,47</t>
+          <t>36,78; 49,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,7; 39,62</t>
+          <t>28,33; 39,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,84; 51,37</t>
+          <t>40,85; 50,82</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,6; 47,67</t>
+          <t>35,14; 47,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,91; 33,28</t>
+          <t>22,69; 33,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,67; 48,48</t>
+          <t>38,02; 48,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,6; 47,67</t>
+          <t>35,14; 47,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,91; 33,28</t>
+          <t>22,69; 33,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,67; 48,48</t>
+          <t>38,02; 48,43</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,43; 33,12</t>
+          <t>19,91; 32,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,72; 17,65</t>
+          <t>6,43; 17,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,92; 30,47</t>
+          <t>16,14; 30,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,43; 33,12</t>
+          <t>19,91; 32,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,72; 17,65</t>
+          <t>6,43; 17,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,92; 30,47</t>
+          <t>16,14; 30,18</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,55; 25,78</t>
+          <t>18,79; 25,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,67; 17,26</t>
+          <t>11,66; 17,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,71; 25,08</t>
+          <t>17,57; 23,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,55; 25,78</t>
+          <t>18,79; 25,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,67; 17,26</t>
+          <t>11,66; 17,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,71; 25,08</t>
+          <t>17,57; 23,85</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -955,39 +955,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,53; 18,74</t>
+          <t>12,63; 18,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 9,06</t>
+          <t>4,53; 9,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 12,73</t>
+          <t>9,15; 14,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,53; 18,74</t>
+          <t>12,63; 18,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 9,06</t>
+          <t>4,53; 9,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 12,73</t>
+          <t>9,15; 14,2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -1035,32 +1035,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,94; 20,55</t>
+          <t>14,92; 20,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,55</t>
+          <t>8,92; 13,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,05; 18,29</t>
+          <t>10,73; 17,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,94; 20,55</t>
+          <t>14,92; 20,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,55</t>
+          <t>8,92; 13,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,05; 18,29</t>
+          <t>10,73; 17,59</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -1115,32 +1115,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,19; 25,73</t>
+          <t>22,29; 25,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,03; 16,8</t>
+          <t>14,1; 16,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,06; 24,85</t>
+          <t>22,25; 25,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,19; 25,73</t>
+          <t>22,29; 25,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,03; 16,8</t>
+          <t>14,1; 16,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,06; 24,85</t>
+          <t>22,25; 25,45</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124871</t>
+          <t>136515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>124871</t>
+          <t>136515</t>
         </is>
       </c>
     </row>
@@ -1342,32 +1342,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>105390; 140233</t>
+          <t>104273; 139880</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>88529; 122197</t>
+          <t>87370; 121199</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>111561; 140322</t>
+          <t>121531; 151175</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105390; 140233</t>
+          <t>104273; 139880</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>88529; 122197</t>
+          <t>87370; 121199</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>111561; 140322</t>
+          <t>121531; 151175</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102447</t>
+          <t>114253</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>102447</t>
+          <t>114253</t>
         </is>
       </c>
     </row>
@@ -1460,32 +1460,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97679; 134602</t>
+          <t>99210; 135405</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76550; 111193</t>
+          <t>75810; 111302</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89357; 115003</t>
+          <t>101059; 128708</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97679; 134602</t>
+          <t>99210; 135405</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76550; 111193</t>
+          <t>75810; 111302</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89357; 115003</t>
+          <t>101059; 128708</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>23678</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>23678</t>
         </is>
       </c>
     </row>
@@ -1578,32 +1578,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43975; 71308</t>
+          <t>42865; 69404</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9528; 25031</t>
+          <t>9123; 24211</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15175; 29037</t>
+          <t>16949; 31700</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43975; 71308</t>
+          <t>42865; 69404</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9528; 25031</t>
+          <t>9123; 24211</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15175; 29037</t>
+          <t>16949; 31700</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94031</t>
+          <t>103191</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94031</t>
+          <t>103191</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>114414; 158983</t>
+          <t>115864; 157825</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80406; 118904</t>
+          <t>80362; 118834</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79189; 112135</t>
+          <t>87560; 118854</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>114414; 158983</t>
+          <t>115864; 157825</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>80406; 118904</t>
+          <t>80362; 118834</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79189; 112135</t>
+          <t>87560; 118854</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>55292</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>55292</t>
         </is>
       </c>
     </row>
@@ -1814,39 +1814,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>74912; 112071</t>
+          <t>75544; 113088</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25911; 51429</t>
+          <t>25729; 51689</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33710; 68247</t>
+          <t>43559; 67620</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74912; 112071</t>
+          <t>75544; 113088</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25911; 51429</t>
+          <t>25729; 51689</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33710; 68247</t>
+          <t>43559; 67620</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53966</t>
+          <t>57291</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53966</t>
+          <t>57291</t>
         </is>
       </c>
     </row>
@@ -1932,32 +1932,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>110579; 152074</t>
+          <t>110457; 153346</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64656; 98221</t>
+          <t>64621; 98644</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42349; 70111</t>
+          <t>44869; 73528</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>110579; 152074</t>
+          <t>110457; 153346</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>64656; 98221</t>
+          <t>64621; 98644</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42349; 70111</t>
+          <t>44869; 73528</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>448113</t>
+          <t>490220</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>448113</t>
+          <t>490220</t>
         </is>
       </c>
     </row>
@@ -2050,32 +2050,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>607037; 703914</t>
+          <t>609765; 701918</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>388046; 464711</t>
+          <t>389853; 467916</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>395698; 490137</t>
+          <t>458600; 524542</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>607037; 703914</t>
+          <t>609765; 701918</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>388046; 464711</t>
+          <t>389853; 467916</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>395698; 490137</t>
+          <t>458600; 524542</t>
         </is>
       </c>
     </row>
